--- a/Task Report/Work item list/work list excell/Other excell/updated VSA tasks.xlsx
+++ b/Task Report/Work item list/work list excell/Other excell/updated VSA tasks.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shahid Raza\Capitall\VSA project functionality\Task Report\Work item list\work list excell\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shahid Raza\Capitall\VSA project functionality\Task Report\Work item list\work list excell\Other excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C0EB33-28E0-4ABA-AC4A-CB8830E99B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B2E3F0-3AC7-4C8C-A755-76F03BC58EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{65BD65AB-347B-4BAB-9C5F-30C021D0C3BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$B$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -158,32 +161,14 @@
     <t>Planning visit on Wednesday</t>
   </si>
   <si>
-    <t>estimated timelines</t>
-  </si>
-  <si>
-    <t>1 Days</t>
-  </si>
-  <si>
-    <t>need to discuss</t>
-  </si>
-  <si>
-    <t>1 days</t>
-  </si>
-  <si>
     <t>deployed</t>
-  </si>
-  <si>
-    <t>Bahadur</t>
-  </si>
-  <si>
-    <t>Prashant</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +206,24 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -301,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -319,6 +322,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -683,9 +695,7 @@
       <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
@@ -771,7 +781,7 @@
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -789,7 +799,7 @@
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -801,9 +811,7 @@
       <c r="E9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>42</v>
-      </c>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
@@ -816,7 +824,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -832,7 +840,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -841,7 +849,7 @@
       <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -857,7 +865,7 @@
       <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -880,7 +888,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -905,7 +913,7 @@
       <c r="A16" s="4">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -921,7 +929,7 @@
       <c r="A17" s="4">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -931,9 +939,7 @@
         <v>28</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
@@ -955,7 +961,7 @@
       <c r="A19" s="4">
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -967,9 +973,7 @@
       <c r="E19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4">
@@ -1023,7 +1027,7 @@
       <c r="A23" s="4">
         <v>21</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1033,15 +1037,13 @@
         <v>17</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1051,9 +1053,7 @@
         <v>36</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
-        <v>42</v>
-      </c>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
@@ -1069,9 +1069,7 @@
         <v>36</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
@@ -1087,26 +1085,17 @@
         <v>39</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="F26" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B26" xr:uid="{CAC6D6C0-AD37-4D97-8537-BFB732A57384}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="affe18f8-2c16-492b-9b47-5374ed54faa0" xsi:nil="true"/>
@@ -1114,7 +1103,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008034D6D5FD3F314393BD3DED1E7D912D" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac3e49493af0d70e377155e6b8349f5c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="affe18f8-2c16-492b-9b47-5374ed54faa0" xmlns:ns4="27a551d9-798f-4814-b65e-8370286c1742" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29c0e58eaa008cebc2391949e27aaa74" ns3:_="" ns4:_="">
     <xsd:import namespace="affe18f8-2c16-492b-9b47-5374ed54faa0"/>
@@ -1303,15 +1292,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6207E42C-8419-4469-A8FA-ECD0B52B83C8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA7E9626-5B53-42C7-9423-19A41154702D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1328,7 +1318,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E9E5FA-4792-4AB8-82B7-A4A8B7563D09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1345,4 +1335,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6207E42C-8419-4469-A8FA-ECD0B52B83C8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>